--- a/fixtures/demo-project/imports/02-wps.xlsx
+++ b/fixtures/demo-project/imports/02-wps.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,6 +421,9 @@
       <c r="G1" t="str">
         <v>Thickness To</v>
       </c>
+      <c r="H1" t="str">
+        <v>Approved On</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -444,6 +447,9 @@
       <c r="G2">
         <v>40</v>
       </c>
+      <c r="H2" t="str">
+        <v>2026-07-31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -467,6 +473,9 @@
       <c r="G3">
         <v>20</v>
       </c>
+      <c r="H3" t="str">
+        <v>2026-07-31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -490,6 +499,9 @@
       <c r="G4">
         <v>40</v>
       </c>
+      <c r="H4" t="str">
+        <v>2026-07-31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -513,10 +525,13 @@
       <c r="G5">
         <v>20</v>
       </c>
+      <c r="H5" t="str">
+        <v>2026-07-31</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>